--- a/artfynd/A 16050-2024 artfynd.xlsx
+++ b/artfynd/A 16050-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117929467</v>
+        <v>117928869</v>
       </c>
       <c r="B2" t="n">
         <v>90782</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585761</v>
+        <v>585839</v>
       </c>
       <c r="R2" t="n">
-        <v>6980243</v>
+        <v>6980230</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117929411</v>
+        <v>117929784</v>
       </c>
       <c r="B3" t="n">
-        <v>103338</v>
+        <v>90782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585800</v>
+        <v>585834</v>
       </c>
       <c r="R3" t="n">
-        <v>6980232</v>
+        <v>6980216</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117929784</v>
+        <v>117929411</v>
       </c>
       <c r="B4" t="n">
-        <v>90782</v>
+        <v>103338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585834</v>
+        <v>585800</v>
       </c>
       <c r="R4" t="n">
-        <v>6980216</v>
+        <v>6980232</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117929216</v>
+        <v>117929530</v>
       </c>
       <c r="B5" t="n">
-        <v>100007</v>
+        <v>90782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585787</v>
+        <v>585761</v>
       </c>
       <c r="R5" t="n">
-        <v>6980277</v>
+        <v>6980243</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117929159</v>
+        <v>117929216</v>
       </c>
       <c r="B6" t="n">
-        <v>90782</v>
+        <v>100007</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585793</v>
+        <v>585787</v>
       </c>
       <c r="R6" t="n">
-        <v>6980241</v>
+        <v>6980277</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117928869</v>
+        <v>117929159</v>
       </c>
       <c r="B7" t="n">
         <v>90782</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585839</v>
+        <v>585793</v>
       </c>
       <c r="R7" t="n">
-        <v>6980230</v>
+        <v>6980241</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117935939</v>
+        <v>117935786</v>
       </c>
       <c r="B9" t="n">
         <v>90782</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585747</v>
+        <v>585760</v>
       </c>
       <c r="R9" t="n">
-        <v>6980187</v>
+        <v>6980242</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117935786</v>
+        <v>117935939</v>
       </c>
       <c r="B10" t="n">
         <v>90782</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585760</v>
+        <v>585747</v>
       </c>
       <c r="R10" t="n">
-        <v>6980242</v>
+        <v>6980187</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117936465</v>
+        <v>117936216</v>
       </c>
       <c r="B11" t="n">
         <v>90782</v>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585799</v>
+        <v>585773</v>
       </c>
       <c r="R11" t="n">
-        <v>6980166</v>
+        <v>6980091</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117936216</v>
+        <v>117936465</v>
       </c>
       <c r="B12" t="n">
         <v>90782</v>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585773</v>
+        <v>585799</v>
       </c>
       <c r="R12" t="n">
-        <v>6980091</v>
+        <v>6980166</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 16050-2024 artfynd.xlsx
+++ b/artfynd/A 16050-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117928869</v>
+        <v>117929216</v>
       </c>
       <c r="B2" t="n">
-        <v>90782</v>
+        <v>100009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585839</v>
+        <v>585787</v>
       </c>
       <c r="R2" t="n">
-        <v>6980230</v>
+        <v>6980277</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117929784</v>
+        <v>117929159</v>
       </c>
       <c r="B3" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585834</v>
+        <v>585793</v>
       </c>
       <c r="R3" t="n">
-        <v>6980216</v>
+        <v>6980241</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -882,7 +882,7 @@
         <v>117929411</v>
       </c>
       <c r="B4" t="n">
-        <v>103338</v>
+        <v>103340</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117929530</v>
+        <v>117929784</v>
       </c>
       <c r="B5" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585761</v>
+        <v>585834</v>
       </c>
       <c r="R5" t="n">
-        <v>6980243</v>
+        <v>6980216</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117929216</v>
+        <v>117929467</v>
       </c>
       <c r="B6" t="n">
-        <v>100007</v>
+        <v>90784</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585787</v>
+        <v>585761</v>
       </c>
       <c r="R6" t="n">
-        <v>6980277</v>
+        <v>6980243</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117929159</v>
+        <v>117928869</v>
       </c>
       <c r="B7" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585793</v>
+        <v>585839</v>
       </c>
       <c r="R7" t="n">
-        <v>6980241</v>
+        <v>6980230</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117936749</v>
+        <v>117936216</v>
       </c>
       <c r="B8" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585845</v>
+        <v>585773</v>
       </c>
       <c r="R8" t="n">
-        <v>6980250</v>
+        <v>6980091</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117935786</v>
+        <v>117936749</v>
       </c>
       <c r="B9" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,13 +1429,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585760</v>
+        <v>585845</v>
       </c>
       <c r="R9" t="n">
-        <v>6980242</v>
+        <v>6980250</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117935939</v>
+        <v>117935786</v>
       </c>
       <c r="B10" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585747</v>
+        <v>585760</v>
       </c>
       <c r="R10" t="n">
-        <v>6980187</v>
+        <v>6980242</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117936216</v>
+        <v>117936465</v>
       </c>
       <c r="B11" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585773</v>
+        <v>585799</v>
       </c>
       <c r="R11" t="n">
-        <v>6980091</v>
+        <v>6980166</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117936465</v>
+        <v>117935939</v>
       </c>
       <c r="B12" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585799</v>
+        <v>585747</v>
       </c>
       <c r="R12" t="n">
-        <v>6980166</v>
+        <v>6980187</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
